--- a/artfynd/A 28150-2026 artfynd.xlsx
+++ b/artfynd/A 28150-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689540</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689591</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403678</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166473</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689560</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825469</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689567</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1786,6 +1836,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689568</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1897,6 +1952,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689569</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342445</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2119,6 +2184,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342454</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825479</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2341,6 +2416,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689565</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689566</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2558,6 +2643,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403132</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2669,6 +2759,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342441</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2780,6 +2875,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342447</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2891,6 +2991,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342448</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3002,6 +3107,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342452</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3113,6 +3223,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342455</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3224,6 +3339,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825475</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3335,6 +3455,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689549</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3446,6 +3571,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689550</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3557,6 +3687,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689552</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3663,6 +3798,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403133</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3774,6 +3914,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342442</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3885,6 +4030,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825478</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3991,6 +4141,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825465</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4103,6 +4258,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342453</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4209,6 +4369,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403033</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4313,6 +4478,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403034</t>
         </is>
       </c>
     </row>
@@ -4426,6 +4596,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342465</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4532,6 +4707,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342459</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4638,6 +4818,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865984</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4744,6 +4929,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403140</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4854,6 +5044,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865917</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4960,6 +5155,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402982</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5066,6 +5266,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402983</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5172,6 +5377,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402984</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5278,6 +5488,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403051</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5394,6 +5609,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121698034</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5500,6 +5720,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87865978</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5606,6 +5831,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403119</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5712,6 +5942,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403120</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5818,6 +6053,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402981</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5924,6 +6164,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403100</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6030,6 +6275,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403102</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6136,6 +6386,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342463</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6242,6 +6497,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402986</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6348,6 +6608,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402987</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6454,6 +6719,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342457</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6556,8 +6826,69 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166372</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>